--- a/www/download/COUNTRY.MEX.WIOD16.xlsx
+++ b/www/download/COUNTRY.MEX.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>México</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>9.45304620797337</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>9.33715504647754</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>9.63706782238553</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>10.780741200744</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>11.282543039666</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>10.8937563812771</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>10.8944329024199</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>10.9272419594062</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>11.031427427225</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>13.4917261232782</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>12.6321320584262</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>12.3780604313052</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>13.1601110056932</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>12.7656368539897</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>13.2816764246078</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>31.748</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>31.448</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>31.609</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>33.468</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>34.829</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>35.203</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>36.683</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>37.417</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>37.982</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>36.633</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>37.267</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>37.792</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>38.861</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>38.612</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>38.997</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>21.181</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20.864</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>20.909</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>22.341</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>23.175</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>23.507</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>24.43</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>24.911</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>25.334</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>24.363</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>24.702</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>25.135</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>25.699</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>25.686</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>67764.535</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>66516.442</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>66853.296</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>70413.953</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>73379.424</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>73758.407</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>76765.912</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>78827.94</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>80011.524</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>77833.22</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>79252.704</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>80303.237</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>82882.043</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>82579.654</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>83500.643</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>45028.956</t>
+          <t>76061295362.1832</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>44016.188</t>
+          <t>74966556992.956</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>44192.875</t>
+          <t>74631780457.8012</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>47127.747</t>
+          <t>75026272624.9447</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>49012.635</t>
+          <t>77980673830.7013</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>49276.815</t>
+          <t>77958801541.6197</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>51115.588</t>
+          <t>81546841433.0344</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>52515.988</t>
+          <t>82517357892.6018</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>53341.374</t>
+          <t>82516507407.884</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>51630.229</t>
+          <t>78661304021.0754</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>52437.734</t>
+          <t>81003544651.1985</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>53275.677</t>
+          <t>82186818002.2328</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>54650.62</t>
+          <t>84218654215.6551</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>54220.142</t>
+          <t>84193579777.3679</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>54796.975</t>
+          <t>84615591527.1686</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>10918833316.9135</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>11626129153.9358</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>12161722200.5059</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>11911055788.6686</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>11548589966.3917</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>11568388393.2323</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>11674263685.269</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>11727709496.4837</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>11306190129.7508</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>11035369500.4475</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>10967743199.983</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>10928692567.2892</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>11162798769.7275</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>11403096530.9203</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>11413188131.449</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3187723.92813294</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3006295.41128399</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2984051.21957392</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3114807.4074291</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>3005135.05639507</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2709649.05686266</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2562359.20119026</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2398643.45245506</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2281240.9686968</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2704766.43215316</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2397729.94361657</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2230230.67337191</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2237776.59349869</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2116791.87079778</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2132531.77937081</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>356067.236738679</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>341727.527590508</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>339515.08907148</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>379640.200066852</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>443057.370787988</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>472982.937254972</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>524711.277317445</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>604706.435914779</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>666303.48444104</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>576037.504437638</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>649660.883022791</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>693873.44919053</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>695153.722952088</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>685129.438939247</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>695497.389678455</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>618025.875840788</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>603405.345249499</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>604316.199634441</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>661151.747284779</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>759739.552743118</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>815486.565654301</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>901159.134259637</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1029576.9278164</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1117491.39030759</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>969443.540193991</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1106009.57602913</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1191702.5382499</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1189841.21798007</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1188304.67991198</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1199793.18511129</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3.12397137066367</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2.7859710155636</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2.63376783907805</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2.95663892741014</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>3.24403629729993</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>3.25960931851386</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>3.37848496299597</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>3.47794072796106</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>3.71789111874554</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3.67861352516617</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>3.78108696054093</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3.87484451337393</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>3.89578116808909</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>3.75486126535704</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>3.80119790972404</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>167402.603970982</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>180064.651385406</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>183856.637013725</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>179342.923118187</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>188274.819230884</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>209203.04273962</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>229244.707619988</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>244448.868163421</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>265504.860030377</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>235395.419560812</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>262304.946133162</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>288434.993826294</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>292999.497955436</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>308170.764767338</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>311932.689424559</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9.45304620797337</t>
+          <t>515.504452905337</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>9.33715504647754</t>
+          <t>557.247278581664</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.63706782238553</t>
+          <t>581.641739267417</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>10.780741200744</t>
+          <t>533.1500308165</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>11.282543039666</t>
+          <t>498.326732382988</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>10.8937563812771</t>
+          <t>492.132457855014</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>10.8944329024199</t>
+          <t>477.867767522498</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>10.9272419594062</t>
+          <t>470.784372224467</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>11.031427427225</t>
+          <t>446.282310211074</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>13.4917261232782</t>
+          <t>452.947549340181</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>12.6321320584262</t>
+          <t>444.004804982191</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>12.3780604313052</t>
+          <t>434.795268976485</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>13.1601110056932</t>
+          <t>434.360236684389</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>12.7656368539897</t>
+          <t>448.052236048575</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>13.2816764246078</t>
+          <t>444.338398756207</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>754710070.060565</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>1967668954.75838</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>3588649123.26995</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>2436943992.95546</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>2366475281.52635</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>3132829877.34401</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>3798356188.65083</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>3231811469.08957</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>2658688802.56601</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>-70984103.1885472</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>1437266941.49953</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>3115776827.01946</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>2735882107.57034</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>2477011838.06089</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1522037370.42937</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>845231832.206042</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>2107411105.57863</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>3846853698.16656</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>3280730828.43201</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>3307287359.83332</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>3913699108.12848</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>4543939042.42693</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>3928543920.82605</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>3465737631.98734</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>1118495541.73004</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>2432061921.82564</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>4204429095.52994</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>3974472734.33038</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>3569470183.21494</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>2815023423.06684</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.723</t>
+          <t>-90521762.1454772</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.879</t>
+          <t>-139742150.820255</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.942</t>
+          <t>-258204574.896609</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.906</t>
+          <t>-843786835.476545</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-940812078.306973</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>-780869230.784461</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.433</t>
+          <t>-745582853.776093</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2.591</t>
+          <t>-696732451.736481</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.827</t>
+          <t>-807048829.421331</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.505</t>
+          <t>-1189479644.91859</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2.806</t>
+          <t>-994794980.32611</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>3.079</t>
+          <t>-1088652268.51048</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>3.118</t>
+          <t>-1238590626.76004</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-1092458345.15405</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>3.293</t>
+          <t>-1292986052.63747</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.093</t>
+          <t>2125.92560523125</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.145</t>
+          <t>2109.72204521187</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.188</t>
+          <t>2113.55104601536</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.164</t>
+          <t>2109.48216607848</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>2114.91674014827</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>2096.29200342235</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>2092.33683439771</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.734</t>
+          <t>2108.14451447152</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>2105.51134779807</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.473</t>
+          <t>2119.16653053384</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.741</t>
+          <t>2122.82558351787</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.961</t>
+          <t>2119.55933141096</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2126.53266692615</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2.104</t>
+          <t>2130.42622204398</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2133.35659131843</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>2134.4360084264</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>2115.11644494058</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>2115.01916672867</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.677</t>
+          <t>2103.93848958845</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>2106.85375995987</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>2095.2013036211</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>2092.66447676272</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.003</t>
+          <t>2106.72921135487</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.082</t>
+          <t>2106.56300444543</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>2124.66567813711</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.007</t>
+          <t>2126.59943769054</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>2124.84654289207</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.149</t>
+          <t>2132.8081221417</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>2138.69696015555</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1.228</t>
+          <t>2141.219850014</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>170881.081360836</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>162555.538919027</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>165015.376471482</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>168195.832110599</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>191269.551559849</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>218390.726281824</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>254350.173110254</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>276555.630849681</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>295083.774930813</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>231121.792654395</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>294695.689895568</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>342497.966625352</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>352024.918236554</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>362137.798411377</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>368185.257722264</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>11072307248.4965</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10390062945.9596</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>10492278173.1434</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>11470963071.8246</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>12501267352.2455</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>12917042786.2531</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>14170745948.2399</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>13919968272.8443</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>13753188934.744</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>13564791383.3969</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>14686113099.7623</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>15600724959.4332</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>15717983927.086</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>16275379718.3252</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>17074544375.7572</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>169542.528076759</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>163625.916798272</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>163864.386729149</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>166116.096556827</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>191929.527433748</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>216113.292865955</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>248107.2120951</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>271147.808433412</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>296266.259163886</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>228022.134691346</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>287056.631128684</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>334098.226441282</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>341552.159745685</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>351267.448786752</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>361452.261312641</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>67764.535</t>
+          <t>11620209566.6962</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>66516.442</t>
+          <t>12529088576.6906</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>66853.296</t>
+          <t>13895070577.7319</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>70413.953</t>
+          <t>13591482404.1913</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>73379.424</t>
+          <t>14958815995.4479</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>73758.407</t>
+          <t>15762706372.5183</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>76765.912</t>
+          <t>17252616517.9912</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>78827.94</t>
+          <t>16622890918.1037</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>80011.524</t>
+          <t>16513679559.8158</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>77833.22</t>
+          <t>13192056072.0263</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>79252.704</t>
+          <t>15462733009.1331</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>80303.237</t>
+          <t>18027308786.5651</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>82882.043</t>
+          <t>17585370110.2899</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>82579.654</t>
+          <t>17845911976.5354</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>83500.643</t>
+          <t>18040597384.1649</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>45028.956</t>
+          <t>1338.55328407737</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>44016.188</t>
+          <t>-1070.37787924491</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>44192.875</t>
+          <t>1150.98974233209</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>47127.747</t>
+          <t>2079.73555377151</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>49012.635</t>
+          <t>-659.975873898799</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>49276.815</t>
+          <t>2277.43341586881</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>51115.588</t>
+          <t>6242.96101515355</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>52515.988</t>
+          <t>5407.82241626885</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>53341.374</t>
+          <t>-1182.48423307253</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>51630.229</t>
+          <t>3099.65796304968</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>52437.734</t>
+          <t>7639.05876688435</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>53275.677</t>
+          <t>8399.74018407046</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>54650.62</t>
+          <t>10472.7584908691</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>54220.142</t>
+          <t>10870.3496246244</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>54796.975</t>
+          <t>6732.99640962344</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>76063.501</t>
+          <t>-547902318.199653</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>74978.157</t>
+          <t>-2139025630.73106</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>74644.033</t>
+          <t>-3402792404.58848</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>75030.433</t>
+          <t>-2120519332.36666</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>77985.678</t>
+          <t>-2457548643.20241</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>77965.015</t>
+          <t>-2845663586.26519</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>81550.897</t>
+          <t>-3081870569.75133</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>82531.618</t>
+          <t>-2702922645.25946</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>82522.877</t>
+          <t>-2760490625.07185</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>78665.003</t>
+          <t>372735311.370613</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>81012.14</t>
+          <t>-776619909.370765</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>82200.415</t>
+          <t>-2426583827.13195</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>84224.075</t>
+          <t>-1867386183.20393</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>84195.039</t>
+          <t>-1570532258.21012</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>84614.762</t>
+          <t>-966053008.40773</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>320070.185190243</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>338794.270284835</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>349094.097738509</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.661</t>
+          <t>336539.698662634</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>373281.439937092</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>416335.521184772</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>475820.17295272</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>510858.274730117</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>554552.07749075</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>426550.544619381</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.106</t>
+          <t>509534.605570714</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1.192</t>
+          <t>582577.724122347</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>594988.487552545</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1.188</t>
+          <t>609020.875085791</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>617337.802783074</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>43821.685</t>
+          <t>0.130136084615835</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>42455.932</t>
+          <t>0.124124210946681</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>41929.4</t>
+          <t>0.12638577358465</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>43080.865</t>
+          <t>0.129740287636912</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>45475.995</t>
+          <t>0.14298348461903</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>45216.175</t>
+          <t>0.148948774763695</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>47481.677</t>
+          <t>0.15769760223615</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>48465.322</t>
+          <t>0.162580365614626</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>49200.412</t>
+          <t>0.161371569300515</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>46740.072</t>
+          <t>0.129060649159037</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>47580.813</t>
+          <t>0.145526631684829</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>47853.595</t>
+          <t>0.155020776109811</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>49203.97</t>
+          <t>0.155663756536254</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>48542.685</t>
+          <t>0.154882347847821</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>49050.056</t>
+          <t>0.155178874747304</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>171742.8713083</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>188027.137155134</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>202280.884133982</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>195260.282411858</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>201879.523821809</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>225437.777326331</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>246430.087205737</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.605</t>
+          <t>263754.445363993</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>282464.249866712</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.576</t>
+          <t>235024.781289102</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>264819.135153495</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>289266.548738037</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>292813.589123655</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>314645.170657391</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>319940.303599964</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>10919.16</t>
+          <t>222557.701398238</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>11627.375</t>
+          <t>242996.711723845</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>12162.978</t>
+          <t>260890.203512604</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>11911.637</t>
+          <t>250819.971520876</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>11548.954</t>
+          <t>259967.593334322</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>11569.028</t>
+          <t>288973.009038836</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>11675.046</t>
+          <t>316045.854718983</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>11729.112</t>
+          <t>337437.169451314</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>11306.196</t>
+          <t>360831.526858095</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>11035.66</t>
+          <t>298767.012882749</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>10968.666</t>
+          <t>336592.718104172</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>10930.083</t>
+          <t>366982.102186924</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>11163.307</t>
+          <t>370346.042745876</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>11403.232</t>
+          <t>398158.603851226</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>11413.022</t>
+          <t>404887.611140761</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>312.38</t>
+          <t>1722624.36042529</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>278.56</t>
+          <t>1879112.44835813</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>263.34</t>
+          <t>1942336.83246301</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>295.64</t>
+          <t>1905592.94848892</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>324.39</t>
+          <t>2010008.91075313</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>325.94</t>
+          <t>2219810.17455009</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>337.82</t>
+          <t>2432658.93487484</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>347.74</t>
+          <t>2591383.06842127</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>371.79</t>
+          <t>2826610.31516828</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>367.85</t>
+          <t>2504913.57377432</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>378.07</t>
+          <t>2805901.24956789</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>387.42</t>
+          <t>3079158.84245708</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>389.56</t>
+          <t>3117956.34962214</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>375.48</t>
+          <t>3250163.91711135</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>380.13</t>
+          <t>3292534.20970022</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.188</t>
+          <t>415498.420524641</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.007</t>
+          <t>414576.731733956</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.985</t>
+          <t>420566.574226354</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3.115</t>
+          <t>421632.949390184</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3.005</t>
+          <t>422557.054950369</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>435511.889974158</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.563</t>
+          <t>443818.363100618</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.399</t>
+          <t>453244.388680234</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.282</t>
+          <t>457176.146806905</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.705</t>
+          <t>445594.635809877</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2.398</t>
+          <t>449789.763038717</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2.231</t>
+          <t>457107.077631074</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2.238</t>
+          <t>469388.655435303</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2.117</t>
+          <t>478677.880520519</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2.132</t>
+          <t>486185.12905664</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>326022.496240717</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>324403.48359195</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>328958.530529922</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>330710.395584826</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>330965.224029292</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>342242.552595773</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>347507.789857105</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>355126.520319096</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>358713.884617218</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>351208.815289987</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>353878.529276816</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>359992.180689271</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>369854.68391099</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>376073.39279719</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>381540.74420626</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>391578.193500585</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>413308.001317944</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>429340.380146521</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>426575.100374011</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>475672.897405668</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>539841.04844684</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>612869.188708097</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>665756.874874903</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>721639.402390106</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>558681.19147941</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>670638.303823031</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>765768.587349379</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>778352.296053683</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>811563.783139814</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>822864.443152842</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>45028956000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>44016188000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>44192875000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>47127747000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>49012635000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>49276815000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>51115588000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>52515988000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>53341374000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>51630229000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>52437734000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>53275677000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>54650620000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>54220142000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>54796975000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>67764535433.6991</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>66516442119.8142</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>66853296093.0024</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>70413952732.8604</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>73379424202.5116</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>73758406520.8177</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>76765912043.6864</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>78827939848.0456</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>80011524485.7955</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>77833219858.3709</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>79252704288.2223</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>80303237474.0902</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>82882043350.6905</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>82579653610.9187</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>83500643021.8915</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>43821685015.263</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>42455931779.2968</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>41929399882.0835</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>43080864970.2255</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>45475995286.7534</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>45216174601.7824</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>47481677433.9022</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>48465322060.1672</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>49200411642.2272</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>46740072407.9748</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>47580812577.6006</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>47853595217.6054</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>49203969517.3913</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>48542685264.3783</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>49050056095.9473</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>31748216</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>31448123</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>31608837</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>33467686</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>34828912</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>35203494</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>36683335</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>37417215</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>37982023</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>36633161</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>37267340</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>37792488</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>38860525</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>38612134</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>38996763</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>21180871</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>20863501</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>20909301</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>22340908</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>23174735</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>23506656</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>24429904</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>24911000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>25334166</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>24363460</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>24701857</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>25135261</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>25699403</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>25450373</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>25685802</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>67764535433.6991</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>66516442119.8142</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>66853296093.0024</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>70413952732.8604</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>73379424202.5116</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>73758406520.8177</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>76765912043.6864</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>78827939848.0456</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>80011524485.7955</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>77833219858.3709</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>79252704288.2223</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>80303237474.0902</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>82882043350.6905</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>82579653610.9187</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>83500643021.8915</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>45028956000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>44016188000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>44192875000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>47127747000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>49012635000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>49276815000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>51115588000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>52515988000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>53341374000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>51630229000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>52437734000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>53275677000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>54650620000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>54220142000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>54796975000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1093021.60297776</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1144825.36889574</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1187559.05305344</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1163601.03658961</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1264788.82493296</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1435254.98091125</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1601970.15663729</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1734393.61109023</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1874876.70507398</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1473112.9152775</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1741137.42896123</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1960922.18806455</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2000442.35376764</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2104457.9027096</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2130489.33858109</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>614135.895427753</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>656304.713577284</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>690230.575772909</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>677395.067442502</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>735640.484092552</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>828814.061341095</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>928915.04260097</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1003194.04588196</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1082470.9259848</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>857448.20569631</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1007231.02010645</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1132750.68759739</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1148698.33492421</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1209722.3909078</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1227752.05128193</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2764788.46281861</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2875710.0860133</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>3011204.73284858</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>3312361.15335407</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>3307970.28497678</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>3327644.53663205</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>3423698.50633412</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>3436559.95306035</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3542458.0837068</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>3756860.71862258</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>3749533.45913402</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>3838820.29811897</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>3974402.39012611</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>3926420.43916442</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>4017172.00049154</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
